--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_diff.xlsx
@@ -1,205 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.beta\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_diff</t>
-  </si>
-  <si>
-    <t>LV2_diff</t>
-  </si>
-  <si>
-    <t>LV3_diff</t>
-  </si>
-  <si>
-    <t>LV4_diff</t>
-  </si>
-  <si>
-    <t>LV5_diff</t>
-  </si>
-  <si>
-    <t>LV6_diff</t>
-  </si>
-  <si>
-    <t>LV7_diff</t>
-  </si>
-  <si>
-    <t>LV8_diff</t>
-  </si>
-  <si>
-    <t>LV9_diff</t>
-  </si>
-  <si>
-    <t>LV10_diff</t>
-  </si>
-  <si>
-    <t>LV11_diff</t>
-  </si>
-  <si>
-    <t>LV12_diff</t>
-  </si>
-  <si>
-    <t>LV13_diff</t>
-  </si>
-  <si>
-    <t>LV14_diff</t>
-  </si>
-  <si>
-    <t>LV15_diff</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,52 +61,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -332,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -364,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -399,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -575,2173 +350,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_diff</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_diff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_diff</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_diff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_diff</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_diff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_diff</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_diff</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_diff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_diff</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_diff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>4.2935817500231267E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>8.6658978485017482E-2</v>
+        <v>0.04293581461117464</v>
       </c>
       <c r="D2">
-        <v>0.1215590455052287</v>
+        <v>0.08665900944536539</v>
       </c>
       <c r="E2">
-        <v>0.1574000512940627</v>
+        <v>0.1215590559558551</v>
       </c>
       <c r="F2">
-        <v>0.18840061796888569</v>
+        <v>0.157400046182725</v>
       </c>
       <c r="G2">
-        <v>0.27120802085424089</v>
+        <v>0.1884006134682013</v>
       </c>
       <c r="H2">
-        <v>0.24178671083298919</v>
+        <v>0.2712080207621455</v>
       </c>
       <c r="I2">
-        <v>0.25364392985650253</v>
+        <v>0.2417867112819734</v>
       </c>
       <c r="J2">
-        <v>0.3468226182723278</v>
+        <v>0.2536439267178899</v>
       </c>
       <c r="K2">
-        <v>0.34641463981832132</v>
+        <v>0.346822610000224</v>
       </c>
       <c r="L2">
-        <v>0.38312786172457602</v>
+        <v>0.3464146381325402</v>
       </c>
       <c r="M2">
-        <v>0.39538633331671102</v>
+        <v>0.3831278689649102</v>
       </c>
       <c r="N2">
-        <v>0.40302984708987349</v>
+        <v>0.3953863294133002</v>
       </c>
       <c r="O2">
-        <v>0.39808822878929739</v>
+        <v>0.4030298412722385</v>
       </c>
       <c r="P2">
-        <v>0.37616953621852978</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.3980882123682375</v>
+      </c>
+      <c r="Q2">
+        <v>0.376169510648047</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>6.4347812548356559E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C3">
-        <v>0.1108947752765245</v>
+        <v>0.06434781273403227</v>
       </c>
       <c r="D3">
-        <v>0.52396701449454219</v>
+        <v>0.1108947679796306</v>
       </c>
       <c r="E3">
-        <v>0.37436554530583538</v>
+        <v>0.5239670279102269</v>
       </c>
       <c r="F3">
-        <v>0.37092187572474011</v>
+        <v>0.3743655974093853</v>
       </c>
       <c r="G3">
-        <v>0.33814931650705637</v>
+        <v>0.3709218932574744</v>
       </c>
       <c r="H3">
-        <v>0.3770482452130679</v>
+        <v>0.3381493175366005</v>
       </c>
       <c r="I3">
-        <v>0.42112281538802809</v>
+        <v>0.3770482978835515</v>
       </c>
       <c r="J3">
-        <v>0.40176121612258242</v>
+        <v>0.4211228308496971</v>
       </c>
       <c r="K3">
-        <v>0.39950526889231402</v>
+        <v>0.4017612212767369</v>
       </c>
       <c r="L3">
-        <v>0.42554068247226851</v>
+        <v>0.3995052639677051</v>
       </c>
       <c r="M3">
-        <v>0.45380561904263289</v>
+        <v>0.4255406627464068</v>
       </c>
       <c r="N3">
-        <v>0.52080511001111585</v>
+        <v>0.4538055773049676</v>
       </c>
       <c r="O3">
-        <v>0.56412151846359215</v>
+        <v>0.5208050133384123</v>
       </c>
       <c r="P3">
-        <v>0.55236246888677998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.5641213486385268</v>
+      </c>
+      <c r="Q3">
+        <v>0.5523622250813677</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>3.8366560742450227E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>6.6035040645732845E-2</v>
+        <v>0.03836655912669518</v>
       </c>
       <c r="D4">
-        <v>0.180069158756438</v>
+        <v>0.06603496555376037</v>
       </c>
       <c r="E4">
-        <v>0.1969110072613931</v>
+        <v>0.1800691508905588</v>
       </c>
       <c r="F4">
-        <v>0.37286992199741792</v>
+        <v>0.1969109792428988</v>
       </c>
       <c r="G4">
-        <v>0.33615267790583608</v>
+        <v>0.3728699337991491</v>
       </c>
       <c r="H4">
-        <v>0.31568482581576618</v>
+        <v>0.3361526534668796</v>
       </c>
       <c r="I4">
-        <v>0.35982506108149043</v>
+        <v>0.3156848008634452</v>
       </c>
       <c r="J4">
-        <v>0.36499516543576138</v>
+        <v>0.3598250394008461</v>
       </c>
       <c r="K4">
-        <v>0.386580095136557</v>
+        <v>0.3649951493031904</v>
       </c>
       <c r="L4">
-        <v>0.39368529703722038</v>
+        <v>0.3865800845022569</v>
       </c>
       <c r="M4">
-        <v>0.39163376249085741</v>
+        <v>0.3936852872806732</v>
       </c>
       <c r="N4">
-        <v>0.39084327799462532</v>
+        <v>0.391633747490086</v>
       </c>
       <c r="O4">
-        <v>0.39577926223375431</v>
+        <v>0.3908432597606246</v>
       </c>
       <c r="P4">
-        <v>0.41811685041682972</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.3957792484807099</v>
+      </c>
+      <c r="Q4">
+        <v>0.4181168389189421</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>4.5396257096008218E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C5">
-        <v>0.13758928512125229</v>
+        <v>0.04539625703752226</v>
       </c>
       <c r="D5">
-        <v>0.18511440255207129</v>
+        <v>0.1375892929413574</v>
       </c>
       <c r="E5">
-        <v>0.46659495920847432</v>
+        <v>0.1851143949195339</v>
       </c>
       <c r="F5">
-        <v>0.32767803150853891</v>
+        <v>0.4665949644965773</v>
       </c>
       <c r="G5">
-        <v>0.38137268804680891</v>
+        <v>0.32767803842124</v>
       </c>
       <c r="H5">
-        <v>0.37028209464916839</v>
+        <v>0.3813726828280773</v>
       </c>
       <c r="I5">
-        <v>0.3617132043135915</v>
+        <v>0.3702821002961628</v>
       </c>
       <c r="J5">
-        <v>0.3248829589090223</v>
+        <v>0.3617131983758812</v>
       </c>
       <c r="K5">
-        <v>0.31569187571913959</v>
+        <v>0.3248829697764555</v>
       </c>
       <c r="L5">
-        <v>0.31358623398989549</v>
+        <v>0.3156918619398283</v>
       </c>
       <c r="M5">
-        <v>0.33341892634020021</v>
+        <v>0.3135862126613703</v>
       </c>
       <c r="N5">
-        <v>0.37626966739936363</v>
+        <v>0.3334188851012866</v>
       </c>
       <c r="O5">
-        <v>0.4146740912249432</v>
+        <v>0.3762696221617888</v>
       </c>
       <c r="P5">
-        <v>0.45942596922550699</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.4146740355324952</v>
+      </c>
+      <c r="Q5">
+        <v>0.4594258881785826</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>4.338747677706644E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C6">
-        <v>0.1247875410657992</v>
+        <v>0.043387476859187</v>
       </c>
       <c r="D6">
-        <v>0.18341818319470171</v>
+        <v>0.1247875561206467</v>
       </c>
       <c r="E6">
-        <v>0.43764433856507651</v>
+        <v>0.1834181778326737</v>
       </c>
       <c r="F6">
-        <v>0.26506953686756629</v>
+        <v>0.4376443660845216</v>
       </c>
       <c r="G6">
-        <v>0.26764594237582318</v>
+        <v>0.2650695421107827</v>
       </c>
       <c r="H6">
-        <v>0.25536498001438929</v>
+        <v>0.2676459490992721</v>
       </c>
       <c r="I6">
-        <v>0.25158514513942681</v>
+        <v>0.2553649849056814</v>
       </c>
       <c r="J6">
-        <v>0.2459106920107435</v>
+        <v>0.251585141512765</v>
       </c>
       <c r="K6">
-        <v>0.24733538742339509</v>
+        <v>0.2459106766363874</v>
       </c>
       <c r="L6">
-        <v>0.26311447418192019</v>
+        <v>0.2473353750834771</v>
       </c>
       <c r="M6">
-        <v>0.28069925737692109</v>
+        <v>0.2631144649070923</v>
       </c>
       <c r="N6">
-        <v>0.31128707160766361</v>
+        <v>0.2806992431923241</v>
       </c>
       <c r="O6">
-        <v>0.32234934751311661</v>
+        <v>0.3112870439655253</v>
       </c>
       <c r="P6">
-        <v>0.36019844576434662</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.3223493237771898</v>
+      </c>
+      <c r="Q6">
+        <v>0.3601984276796225</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>4.3462664949083601E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>7.1146610841139213E-2</v>
+        <v>0.04346266349949161</v>
       </c>
       <c r="D7">
-        <v>0.18010898101616279</v>
+        <v>0.07114660972255113</v>
       </c>
       <c r="E7">
-        <v>0.22941863523212139</v>
+        <v>0.180108969295257</v>
       </c>
       <c r="F7">
-        <v>0.30209588296635442</v>
+        <v>0.2294186294980091</v>
       </c>
       <c r="G7">
-        <v>0.41199818370380509</v>
+        <v>0.3020958947545317</v>
       </c>
       <c r="H7">
-        <v>0.34534653965002837</v>
+        <v>0.4119981988731599</v>
       </c>
       <c r="I7">
-        <v>0.32768482724584602</v>
+        <v>0.3453466067288782</v>
       </c>
       <c r="J7">
-        <v>0.4190372783605969</v>
+        <v>0.3276848356266695</v>
       </c>
       <c r="K7">
-        <v>0.38448714618319668</v>
+        <v>0.4190372564855515</v>
       </c>
       <c r="L7">
-        <v>0.40960423841230947</v>
+        <v>0.3844871172061563</v>
       </c>
       <c r="M7">
-        <v>0.43159973250387917</v>
+        <v>0.4096042242146845</v>
       </c>
       <c r="N7">
-        <v>0.40004016049611668</v>
+        <v>0.4315997068201918</v>
       </c>
       <c r="O7">
-        <v>0.38924785842588039</v>
+        <v>0.4000401251360586</v>
       </c>
       <c r="P7">
-        <v>0.39141557781384312</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.3892478339963804</v>
+      </c>
+      <c r="Q7">
+        <v>0.3914155527610984</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>4.2219072336685849E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>6.521114976922103E-2</v>
+        <v>0.04221907187237935</v>
       </c>
       <c r="D8">
-        <v>0.16774469594701391</v>
+        <v>0.06521115175587058</v>
       </c>
       <c r="E8">
-        <v>0.29097308239357411</v>
+        <v>0.1677446885112774</v>
       </c>
       <c r="F8">
-        <v>0.30650124470600387</v>
+        <v>0.2909730826867856</v>
       </c>
       <c r="G8">
-        <v>0.31085506044742178</v>
+        <v>0.3065012278855117</v>
       </c>
       <c r="H8">
-        <v>0.31696703978265489</v>
+        <v>0.3108550546677036</v>
       </c>
       <c r="I8">
-        <v>0.33598864571347492</v>
+        <v>0.3169670075294205</v>
       </c>
       <c r="J8">
-        <v>0.33742780231681291</v>
+        <v>0.3359886455430648</v>
       </c>
       <c r="K8">
-        <v>0.35268747411139389</v>
+        <v>0.3374278021919846</v>
       </c>
       <c r="L8">
-        <v>0.38577619585584783</v>
+        <v>0.3526874624678435</v>
       </c>
       <c r="M8">
-        <v>0.37800157772235032</v>
+        <v>0.3857761773149155</v>
       </c>
       <c r="N8">
-        <v>0.36205561398444192</v>
+        <v>0.3780015584827929</v>
       </c>
       <c r="O8">
-        <v>0.3783294161896571</v>
+        <v>0.3620555958320347</v>
       </c>
       <c r="P8">
-        <v>0.39751330116919559</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.3783293995283883</v>
+      </c>
+      <c r="Q8">
+        <v>0.3975132718752548</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>3.9879828910231667E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>6.3942188116186724E-2</v>
+        <v>0.03987982855257046</v>
       </c>
       <c r="D9">
-        <v>0.15621849170379279</v>
+        <v>0.06394218835495312</v>
       </c>
       <c r="E9">
-        <v>0.26803683592703631</v>
+        <v>0.1562184813004762</v>
       </c>
       <c r="F9">
-        <v>0.27195862856851238</v>
+        <v>0.2680368390632527</v>
       </c>
       <c r="G9">
-        <v>0.26615228832735682</v>
+        <v>0.2719586221630431</v>
       </c>
       <c r="H9">
-        <v>0.26760720115898889</v>
+        <v>0.2661522829513528</v>
       </c>
       <c r="I9">
-        <v>0.27691240090898789</v>
+        <v>0.2676072062911382</v>
       </c>
       <c r="J9">
-        <v>0.26565899799032672</v>
+        <v>0.2769123973189402</v>
       </c>
       <c r="K9">
-        <v>0.2451697147164279</v>
+        <v>0.2656589882592745</v>
       </c>
       <c r="L9">
-        <v>0.27957557854231269</v>
+        <v>0.2451697122451177</v>
       </c>
       <c r="M9">
-        <v>0.26095368650093081</v>
+        <v>0.2795755766639241</v>
       </c>
       <c r="N9">
-        <v>0.249284736915002</v>
+        <v>0.2609536839127876</v>
       </c>
       <c r="O9">
-        <v>0.25402355116296071</v>
+        <v>0.2492847369029124</v>
       </c>
       <c r="P9">
-        <v>0.27949945674115312</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.2540235589850026</v>
+      </c>
+      <c r="Q9">
+        <v>0.2794994721629457</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>3.8213199905875003E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>6.1769049813525642E-2</v>
+        <v>0.03821319971399598</v>
       </c>
       <c r="D10">
-        <v>0.165089390266728</v>
+        <v>0.06176904897273389</v>
       </c>
       <c r="E10">
-        <v>0.26934777009283539</v>
+        <v>0.1650893796574975</v>
       </c>
       <c r="F10">
-        <v>0.27940932668750079</v>
+        <v>0.2693477715419097</v>
       </c>
       <c r="G10">
-        <v>0.27253504101947001</v>
+        <v>0.2794093164547664</v>
       </c>
       <c r="H10">
-        <v>0.26642526856610382</v>
+        <v>0.272535033277015</v>
       </c>
       <c r="I10">
-        <v>0.27416862411646797</v>
+        <v>0.2664252682407621</v>
       </c>
       <c r="J10">
-        <v>0.26867604681826163</v>
+        <v>0.2741686138456712</v>
       </c>
       <c r="K10">
-        <v>0.25093642668347871</v>
+        <v>0.2686760336863622</v>
       </c>
       <c r="L10">
-        <v>0.28737976630909268</v>
+        <v>0.2509364204938325</v>
       </c>
       <c r="M10">
-        <v>0.2702297361595285</v>
+        <v>0.287379764015948</v>
       </c>
       <c r="N10">
-        <v>0.26145805496011298</v>
+        <v>0.2702297386460828</v>
       </c>
       <c r="O10">
-        <v>0.26222657603919891</v>
+        <v>0.2614580609595238</v>
       </c>
       <c r="P10">
-        <v>0.2855063935577869</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.262226583523719</v>
+      </c>
+      <c r="Q10">
+        <v>0.2855064015685614</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>4.3251474635265658E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>6.8186631803990705E-2</v>
+        <v>0.04325147468162663</v>
       </c>
       <c r="D11">
-        <v>0.1638021419563063</v>
+        <v>0.0681866318777405</v>
       </c>
       <c r="E11">
-        <v>0.27223438247187232</v>
+        <v>0.1638021315467235</v>
       </c>
       <c r="F11">
-        <v>0.27573399722945863</v>
+        <v>0.2722343833240327</v>
       </c>
       <c r="G11">
-        <v>0.27304150763915758</v>
+        <v>0.2757339819934208</v>
       </c>
       <c r="H11">
-        <v>0.27599215355044898</v>
+        <v>0.2730415104235383</v>
       </c>
       <c r="I11">
-        <v>0.27286984749441662</v>
+        <v>0.2759921681411209</v>
       </c>
       <c r="J11">
-        <v>0.26721214113558828</v>
+        <v>0.2728698384098911</v>
       </c>
       <c r="K11">
-        <v>0.24085342429286391</v>
+        <v>0.2672121203285722</v>
       </c>
       <c r="L11">
-        <v>0.2718006986614761</v>
+        <v>0.2408534443500314</v>
       </c>
       <c r="M11">
-        <v>0.25834127731036882</v>
+        <v>0.2718006974915375</v>
       </c>
       <c r="N11">
-        <v>0.2486256621128792</v>
+        <v>0.2583412679326273</v>
       </c>
       <c r="O11">
-        <v>0.2583820670654573</v>
+        <v>0.248625655767384</v>
       </c>
       <c r="P11">
-        <v>0.27419993612868238</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.2583820655793718</v>
+      </c>
+      <c r="Q11">
+        <v>0.2741998994763553</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>4.7306232736826173E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C12">
-        <v>0.1446094076247906</v>
+        <v>0.04730623278919534</v>
       </c>
       <c r="D12">
-        <v>0.1578145800666067</v>
+        <v>0.1446094165686259</v>
       </c>
       <c r="E12">
-        <v>0.39115226970301098</v>
+        <v>0.1578145722777368</v>
       </c>
       <c r="F12">
-        <v>0.33489522237022112</v>
+        <v>0.3911522832835826</v>
       </c>
       <c r="G12">
-        <v>0.34384844170281009</v>
+        <v>0.3348952273776599</v>
       </c>
       <c r="H12">
-        <v>0.3381614291749333</v>
+        <v>0.3438484305692184</v>
       </c>
       <c r="I12">
-        <v>0.31170793517803908</v>
+        <v>0.3381614275884565</v>
       </c>
       <c r="J12">
-        <v>0.30027889325653118</v>
+        <v>0.3117079217335254</v>
       </c>
       <c r="K12">
-        <v>0.29877041186417241</v>
+        <v>0.3002788757957247</v>
       </c>
       <c r="L12">
-        <v>0.30186103509520629</v>
+        <v>0.2987703960356608</v>
       </c>
       <c r="M12">
-        <v>0.3189920146731221</v>
+        <v>0.3018610064356929</v>
       </c>
       <c r="N12">
-        <v>0.35460353615871892</v>
+        <v>0.3189919804823138</v>
       </c>
       <c r="O12">
-        <v>0.39287124807613433</v>
+        <v>0.3546034864547538</v>
       </c>
       <c r="P12">
-        <v>0.45529172945674462</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.3928711841590868</v>
+      </c>
+      <c r="Q12">
+        <v>0.455291627107154</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>4.8405333262818047E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C13">
-        <v>0.21328986309586631</v>
+        <v>0.04840533358676906</v>
       </c>
       <c r="D13">
-        <v>0.27213570209588039</v>
+        <v>0.2132898730677752</v>
       </c>
       <c r="E13">
-        <v>0.38277105126073779</v>
+        <v>0.2721356906113034</v>
       </c>
       <c r="F13">
-        <v>0.50028978954772274</v>
+        <v>0.3827710566984354</v>
       </c>
       <c r="G13">
-        <v>0.48517808759609221</v>
+        <v>0.5002898145926031</v>
       </c>
       <c r="H13">
-        <v>0.5579563146911023</v>
+        <v>0.4851781020786097</v>
       </c>
       <c r="I13">
-        <v>0.54128947002417804</v>
+        <v>0.557956328840985</v>
       </c>
       <c r="J13">
-        <v>0.52005095539285928</v>
+        <v>0.5412894768487603</v>
       </c>
       <c r="K13">
-        <v>0.49334016892839688</v>
+        <v>0.5200509380301059</v>
       </c>
       <c r="L13">
-        <v>0.495027742792992</v>
+        <v>0.4933401420649551</v>
       </c>
       <c r="M13">
-        <v>0.50326119435604688</v>
+        <v>0.4950277099516821</v>
       </c>
       <c r="N13">
-        <v>0.50492862241710346</v>
+        <v>0.5032611512283252</v>
       </c>
       <c r="O13">
-        <v>0.51448726508283038</v>
+        <v>0.5049285593085595</v>
       </c>
       <c r="P13">
-        <v>0.55218796228479605</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.5144871634776803</v>
+      </c>
+      <c r="Q13">
+        <v>0.5521878202273833</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>4.0199252903591581E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C14">
-        <v>7.0305039833459995E-2</v>
+        <v>0.04019925032728561</v>
       </c>
       <c r="D14">
-        <v>0.17433561433128261</v>
+        <v>0.07030503599755016</v>
       </c>
       <c r="E14">
-        <v>0.2104311522972783</v>
+        <v>0.1743356056121326</v>
       </c>
       <c r="F14">
-        <v>0.27829598152644619</v>
+        <v>0.2104311449885934</v>
       </c>
       <c r="G14">
-        <v>0.3664923868985327</v>
+        <v>0.2782959812287414</v>
       </c>
       <c r="H14">
-        <v>0.30268273106037857</v>
+        <v>0.3664923970812529</v>
       </c>
       <c r="I14">
-        <v>0.27125204211131748</v>
+        <v>0.3026827283248905</v>
       </c>
       <c r="J14">
-        <v>0.35717196512811572</v>
+        <v>0.2712520362724526</v>
       </c>
       <c r="K14">
-        <v>0.41905139221489601</v>
+        <v>0.3571719520276751</v>
       </c>
       <c r="L14">
-        <v>0.32692378499390728</v>
+        <v>0.4190508844055573</v>
       </c>
       <c r="M14">
-        <v>0.32146446121730748</v>
+        <v>0.3269237319723671</v>
       </c>
       <c r="N14">
-        <v>0.2975097757365307</v>
+        <v>0.3214644522384452</v>
       </c>
       <c r="O14">
-        <v>0.29926229786607278</v>
+        <v>0.2975097656488021</v>
       </c>
       <c r="P14">
-        <v>0.29676107044405808</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.2992622866143277</v>
+      </c>
+      <c r="Q14">
+        <v>0.2967610581979372</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>4.0395869918111733E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C15">
-        <v>6.7003569192856965E-2</v>
+        <v>0.04039586787170074</v>
       </c>
       <c r="D15">
-        <v>0.1688487447439041</v>
+        <v>0.06700356913163223</v>
       </c>
       <c r="E15">
-        <v>0.20531986881050721</v>
+        <v>0.1688487344230049</v>
       </c>
       <c r="F15">
-        <v>0.26693159327821481</v>
+        <v>0.2053198630817367</v>
       </c>
       <c r="G15">
-        <v>0.35097627962248551</v>
+        <v>0.2669315882428454</v>
       </c>
       <c r="H15">
-        <v>0.29300495016355588</v>
+        <v>0.3509762688265294</v>
       </c>
       <c r="I15">
-        <v>0.27090128048877388</v>
+        <v>0.2930053107728008</v>
       </c>
       <c r="J15">
-        <v>0.35519635073235828</v>
+        <v>0.270901998241161</v>
       </c>
       <c r="K15">
-        <v>0.3995425898839533</v>
+        <v>0.3551963254786104</v>
       </c>
       <c r="L15">
-        <v>0.32573821882603871</v>
+        <v>0.3995431098445525</v>
       </c>
       <c r="M15">
-        <v>0.32501432120347579</v>
+        <v>0.3257382204327006</v>
       </c>
       <c r="N15">
-        <v>0.29656035808874631</v>
+        <v>0.325014311453928</v>
       </c>
       <c r="O15">
-        <v>0.29199458253889432</v>
+        <v>0.2965603515198922</v>
       </c>
       <c r="P15">
-        <v>0.29196382736048132</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.2919945717028363</v>
+      </c>
+      <c r="Q15">
+        <v>0.2919638199827663</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>4.0262952902623932E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C16">
-        <v>6.919816339428056E-2</v>
+        <v>0.04026294980222288</v>
       </c>
       <c r="D16">
-        <v>0.17052865070341541</v>
+        <v>0.06919815673726418</v>
       </c>
       <c r="E16">
-        <v>0.2042857926190115</v>
+        <v>0.1705286399722894</v>
       </c>
       <c r="F16">
-        <v>0.27371860442426182</v>
+        <v>0.2042857832024781</v>
       </c>
       <c r="G16">
-        <v>0.35514365431265432</v>
+        <v>0.2737186101190335</v>
       </c>
       <c r="H16">
-        <v>0.29929482008797093</v>
+        <v>0.3551436543127018</v>
       </c>
       <c r="I16">
-        <v>0.26298416096540911</v>
+        <v>0.2992948214909605</v>
       </c>
       <c r="J16">
-        <v>0.34510140220207008</v>
+        <v>0.2629841541873312</v>
       </c>
       <c r="K16">
-        <v>0.32411399175691419</v>
+        <v>0.3451013890129004</v>
       </c>
       <c r="L16">
-        <v>0.31232497212513832</v>
+        <v>0.3241139004971568</v>
       </c>
       <c r="M16">
-        <v>0.30797664875400399</v>
+        <v>0.3123249659174845</v>
       </c>
       <c r="N16">
-        <v>0.27576405665050108</v>
+        <v>0.3079766430031596</v>
       </c>
       <c r="O16">
-        <v>0.2770600697718768</v>
+        <v>0.2757640517834716</v>
       </c>
       <c r="P16">
-        <v>0.27307501729741268</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.2770600658482716</v>
+      </c>
+      <c r="Q16">
+        <v>0.2730750166952029</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>4.4712139802813751E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C17">
-        <v>7.488727236368671E-2</v>
+        <v>0.04471213761685983</v>
       </c>
       <c r="D17">
-        <v>0.17890083033484969</v>
+        <v>0.07488727427190642</v>
       </c>
       <c r="E17">
-        <v>0.21838474875417119</v>
+        <v>0.1789008204967336</v>
       </c>
       <c r="F17">
-        <v>0.27974765913077959</v>
+        <v>0.2183847395803792</v>
       </c>
       <c r="G17">
-        <v>0.36046846262340221</v>
+        <v>0.2797476609999606</v>
       </c>
       <c r="H17">
-        <v>0.30351364694026062</v>
+        <v>0.3604684626296731</v>
       </c>
       <c r="I17">
-        <v>0.27215474602367912</v>
+        <v>0.3035136379814101</v>
       </c>
       <c r="J17">
-        <v>0.36075612733708867</v>
+        <v>0.2721547364189014</v>
       </c>
       <c r="K17">
-        <v>0.3656844633611257</v>
+        <v>0.3607561209120385</v>
       </c>
       <c r="L17">
-        <v>0.33841144205533019</v>
+        <v>0.3656848429075503</v>
       </c>
       <c r="M17">
-        <v>0.32332506047919118</v>
+        <v>0.3384114596713855</v>
       </c>
       <c r="N17">
-        <v>0.30051135179311728</v>
+        <v>0.3233250510373095</v>
       </c>
       <c r="O17">
-        <v>0.2951889752135865</v>
+        <v>0.3005113464189417</v>
       </c>
       <c r="P17">
-        <v>0.28844938001836279</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.2951889684935035</v>
+      </c>
+      <c r="Q17">
+        <v>0.2884493725735743</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>4.4252251334848877E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C18">
-        <v>0.14060862084059589</v>
+        <v>0.04425225125008272</v>
       </c>
       <c r="D18">
-        <v>0.18395072258080911</v>
+        <v>0.1406086302705952</v>
       </c>
       <c r="E18">
-        <v>0.43129458403197868</v>
+        <v>0.1839507251384462</v>
       </c>
       <c r="F18">
-        <v>0.33304020677311269</v>
+        <v>0.4312945967129517</v>
       </c>
       <c r="G18">
-        <v>0.35967996247995743</v>
+        <v>0.3330402046968557</v>
       </c>
       <c r="H18">
-        <v>0.33765350172001729</v>
+        <v>0.3596799615041792</v>
       </c>
       <c r="I18">
-        <v>0.34365512378904989</v>
+        <v>0.3376535047791235</v>
       </c>
       <c r="J18">
-        <v>0.30770628504352898</v>
+        <v>0.3436551194060004</v>
       </c>
       <c r="K18">
-        <v>0.30355242499737511</v>
+        <v>0.3077062852316347</v>
       </c>
       <c r="L18">
-        <v>0.30512617868898262</v>
+        <v>0.3035524853264295</v>
       </c>
       <c r="M18">
-        <v>0.32408814103493011</v>
+        <v>0.3051261530476625</v>
       </c>
       <c r="N18">
-        <v>0.36849052998404602</v>
+        <v>0.3240881106605253</v>
       </c>
       <c r="O18">
-        <v>0.41557641389551359</v>
+        <v>0.3684904878763989</v>
       </c>
       <c r="P18">
-        <v>0.45311002710530768</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.4155763616000516</v>
+      </c>
+      <c r="Q18">
+        <v>0.4531099520760089</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>4.2259474757734922E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>0.1258355061414318</v>
+        <v>0.04225947468614143</v>
       </c>
       <c r="D19">
-        <v>0.19018866329809181</v>
+        <v>0.1258355195988974</v>
       </c>
       <c r="E19">
-        <v>0.44070614944869729</v>
+        <v>0.190188641854123</v>
       </c>
       <c r="F19">
-        <v>0.30131343112013081</v>
+        <v>0.4407061713538292</v>
       </c>
       <c r="G19">
-        <v>0.28151113346340328</v>
+        <v>0.3013134298739908</v>
       </c>
       <c r="H19">
-        <v>0.28020867480730399</v>
+        <v>0.2815111386118608</v>
       </c>
       <c r="I19">
-        <v>0.25802597544524097</v>
+        <v>0.280208677702259</v>
       </c>
       <c r="J19">
-        <v>0.25022120631142519</v>
+        <v>0.2580259721717574</v>
       </c>
       <c r="K19">
-        <v>0.26139113915052647</v>
+        <v>0.2502211946807741</v>
       </c>
       <c r="L19">
-        <v>0.28072296365136268</v>
+        <v>0.2613912659575911</v>
       </c>
       <c r="M19">
-        <v>0.3026073254996145</v>
+        <v>0.2807229554904146</v>
       </c>
       <c r="N19">
-        <v>0.33954782243611947</v>
+        <v>0.3026073140460316</v>
       </c>
       <c r="O19">
-        <v>0.34296362106222772</v>
+        <v>0.3395478125905994</v>
       </c>
       <c r="P19">
-        <v>0.36916902526437978</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.3429636012481984</v>
+      </c>
+      <c r="Q19">
+        <v>0.3691689878533443</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>4.2635650868529287E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>0.1101558086357243</v>
+        <v>0.04263565056913127</v>
       </c>
       <c r="D20">
-        <v>0.2083619920480908</v>
+        <v>0.1101558247063636</v>
       </c>
       <c r="E20">
-        <v>0.28320621758677189</v>
+        <v>0.2083619886118969</v>
       </c>
       <c r="F20">
-        <v>0.24242129090126779</v>
+        <v>0.2832062234873148</v>
       </c>
       <c r="G20">
-        <v>0.32449580972354541</v>
+        <v>0.2424212901395322</v>
       </c>
       <c r="H20">
-        <v>0.2566784138026848</v>
+        <v>0.3244957886538578</v>
       </c>
       <c r="I20">
-        <v>0.24347451492941141</v>
+        <v>0.2566783938589203</v>
       </c>
       <c r="J20">
-        <v>0.2345647092736084</v>
+        <v>0.2434745110854796</v>
       </c>
       <c r="K20">
-        <v>0.22867160041927101</v>
+        <v>0.2345645981145337</v>
       </c>
       <c r="L20">
-        <v>0.24849515369054481</v>
+        <v>0.2286715725871395</v>
       </c>
       <c r="M20">
-        <v>0.29051005053661111</v>
+        <v>0.2484951487196218</v>
       </c>
       <c r="N20">
-        <v>0.2617843977283062</v>
+        <v>0.2905100519578988</v>
       </c>
       <c r="O20">
-        <v>0.28784091081488489</v>
+        <v>0.2617843901178534</v>
       </c>
       <c r="P20">
-        <v>0.30882146081871897</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.2878408913210241</v>
+      </c>
+      <c r="Q20">
+        <v>0.3088214495903215</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>6.2263980303566092E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C21">
-        <v>0.10208700522354019</v>
+        <v>0.06226397968483355</v>
       </c>
       <c r="D21">
-        <v>0.45716587388873281</v>
+        <v>0.1020870004774164</v>
       </c>
       <c r="E21">
-        <v>0.32765588121588862</v>
+        <v>0.4571658966134229</v>
       </c>
       <c r="F21">
-        <v>0.32324135602712212</v>
+        <v>0.3276559074811112</v>
       </c>
       <c r="G21">
-        <v>0.34025627437674871</v>
+        <v>0.3232413909324383</v>
       </c>
       <c r="H21">
-        <v>0.40650910812506891</v>
+        <v>0.3402563110447512</v>
       </c>
       <c r="I21">
-        <v>0.43883582832420021</v>
+        <v>0.4065091086780465</v>
       </c>
       <c r="J21">
-        <v>0.40677707810006941</v>
+        <v>0.4388358037771365</v>
       </c>
       <c r="K21">
-        <v>0.41495505082097389</v>
+        <v>0.4067770612643773</v>
       </c>
       <c r="L21">
-        <v>0.42140172881681931</v>
+        <v>0.4149550167727545</v>
       </c>
       <c r="M21">
-        <v>0.45989197938031562</v>
+        <v>0.4214016686187467</v>
       </c>
       <c r="N21">
-        <v>0.51758939721679642</v>
+        <v>0.4598918821063689</v>
       </c>
       <c r="O21">
-        <v>0.55884157898021791</v>
+        <v>0.5175892773017434</v>
       </c>
       <c r="P21">
-        <v>0.57326078457772867</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.5588413822321153</v>
+      </c>
+      <c r="Q21">
+        <v>0.5732605248983567</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>6.2880643666395356E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C22">
-        <v>0.1051161708099935</v>
+        <v>0.0628806432564214</v>
       </c>
       <c r="D22">
-        <v>0.45921084045842181</v>
+        <v>0.1051161645182158</v>
       </c>
       <c r="E22">
-        <v>0.32211081190591567</v>
+        <v>0.459210857959143</v>
       </c>
       <c r="F22">
-        <v>0.3265228723605868</v>
+        <v>0.3221108408361796</v>
       </c>
       <c r="G22">
-        <v>0.34246993088394961</v>
+        <v>0.326522909637569</v>
       </c>
       <c r="H22">
-        <v>0.41497743886005473</v>
+        <v>0.3424699254793904</v>
       </c>
       <c r="I22">
-        <v>0.461602221560101</v>
+        <v>0.414977419294482</v>
       </c>
       <c r="J22">
-        <v>0.42985116978161703</v>
+        <v>0.4616021784292086</v>
       </c>
       <c r="K22">
-        <v>0.43788160509695051</v>
+        <v>0.4298511137705174</v>
       </c>
       <c r="L22">
-        <v>0.46016475682651559</v>
+        <v>0.4378815493160932</v>
       </c>
       <c r="M22">
-        <v>0.49341082296276723</v>
+        <v>0.4601646782775423</v>
       </c>
       <c r="N22">
-        <v>0.53549778628843303</v>
+        <v>0.4934106814128032</v>
       </c>
       <c r="O22">
-        <v>0.55439188153114638</v>
+        <v>0.5354975430949754</v>
       </c>
       <c r="P22">
-        <v>0.57666240705089833</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.5543915509390815</v>
+      </c>
+      <c r="Q22">
+        <v>0.5766619878916606</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>4.6750661845032758E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C23">
-        <v>0.21514265318494599</v>
+        <v>0.04675066146352748</v>
       </c>
       <c r="D23">
-        <v>0.1820365226877749</v>
+        <v>0.215142736109871</v>
       </c>
       <c r="E23">
-        <v>0.2147221154363316</v>
+        <v>0.1820365742201606</v>
       </c>
       <c r="F23">
-        <v>0.25784158556628839</v>
+        <v>0.2147221312860241</v>
       </c>
       <c r="G23">
-        <v>0.25751733109757441</v>
+        <v>0.257841587600018</v>
       </c>
       <c r="H23">
-        <v>0.27399327841718257</v>
+        <v>0.2575173349956452</v>
       </c>
       <c r="I23">
-        <v>0.30159461435641982</v>
+        <v>0.2739932811993315</v>
       </c>
       <c r="J23">
-        <v>0.30523707923087989</v>
+        <v>0.3015946031725641</v>
       </c>
       <c r="K23">
-        <v>0.3407979421816128</v>
+        <v>0.3052370418578805</v>
       </c>
       <c r="L23">
-        <v>0.37039440829056902</v>
+        <v>0.3407978236010628</v>
       </c>
       <c r="M23">
-        <v>0.4272996077773703</v>
+        <v>0.3703942357205945</v>
       </c>
       <c r="N23">
-        <v>0.45874423165825651</v>
+        <v>0.4272992626873675</v>
       </c>
       <c r="O23">
-        <v>0.49233195499329607</v>
+        <v>0.4587438040163249</v>
       </c>
       <c r="P23">
-        <v>0.53484536665880533</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.4923314851211411</v>
+      </c>
+      <c r="Q23">
+        <v>0.5348447962490643</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>4.3469224710414082E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C24">
-        <v>0.1613631653616466</v>
+        <v>0.04346922479781662</v>
       </c>
       <c r="D24">
-        <v>0.19507734971223381</v>
+        <v>0.1613631737117797</v>
       </c>
       <c r="E24">
-        <v>0.1951054153728434</v>
+        <v>0.1950773412375969</v>
       </c>
       <c r="F24">
-        <v>0.23628574530107499</v>
+        <v>0.1951053955216329</v>
       </c>
       <c r="G24">
-        <v>0.22668994642021081</v>
+        <v>0.2362857418088563</v>
       </c>
       <c r="H24">
-        <v>0.34199089229102209</v>
+        <v>0.2266899577836687</v>
       </c>
       <c r="I24">
-        <v>0.42542339710802429</v>
+        <v>0.3419909142344943</v>
       </c>
       <c r="J24">
-        <v>0.439570508884083</v>
+        <v>0.4254233935146663</v>
       </c>
       <c r="K24">
-        <v>0.43219349251134781</v>
+        <v>0.4395704890326745</v>
       </c>
       <c r="L24">
-        <v>0.44604709099348638</v>
+        <v>0.4321934629147091</v>
       </c>
       <c r="M24">
-        <v>0.53319066097715662</v>
+        <v>0.4460470475439172</v>
       </c>
       <c r="N24">
-        <v>0.65458274324828147</v>
+        <v>0.5331905677336799</v>
       </c>
       <c r="O24">
-        <v>0.73039196245280669</v>
+        <v>0.6545825633654115</v>
       </c>
       <c r="P24">
-        <v>0.8159419196143658</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>0.7303917686271193</v>
+      </c>
+      <c r="Q24">
+        <v>0.8159417041019329</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>4.4086719637755012E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C25">
-        <v>0.17906795339540979</v>
+        <v>0.0440867175430705</v>
       </c>
       <c r="D25">
-        <v>0.20921606045893359</v>
+        <v>0.1790679713444628</v>
       </c>
       <c r="E25">
-        <v>0.20581834623209361</v>
+        <v>0.2092160557136031</v>
       </c>
       <c r="F25">
-        <v>0.2109393413792027</v>
+        <v>0.2058183273237508</v>
       </c>
       <c r="G25">
-        <v>0.24370520631045681</v>
+        <v>0.2109393599754612</v>
       </c>
       <c r="H25">
-        <v>0.36180212686654151</v>
+        <v>0.243705209651167</v>
       </c>
       <c r="I25">
-        <v>0.53175565729759766</v>
+        <v>0.3618021266185436</v>
       </c>
       <c r="J25">
-        <v>0.51756058722435216</v>
+        <v>0.5317556587400866</v>
       </c>
       <c r="K25">
-        <v>0.47293197824689259</v>
+        <v>0.5175605804169318</v>
       </c>
       <c r="L25">
-        <v>0.46829349371037299</v>
+        <v>0.4729319555805026</v>
       </c>
       <c r="M25">
-        <v>0.49643235727921858</v>
+        <v>0.4682934691167783</v>
       </c>
       <c r="N25">
-        <v>0.57882910381413466</v>
+        <v>0.4964322969042369</v>
       </c>
       <c r="O25">
-        <v>0.67961440977603205</v>
+        <v>0.578829023332177</v>
       </c>
       <c r="P25">
-        <v>0.76224541330336137</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>0.6796141013078072</v>
+      </c>
+      <c r="Q25">
+        <v>0.7622451875648995</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>3.960928808895485E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C26">
-        <v>0.1917776342197825</v>
+        <v>0.03960928724159646</v>
       </c>
       <c r="D26">
-        <v>0.18187637712073079</v>
+        <v>0.1917776419358627</v>
       </c>
       <c r="E26">
-        <v>0.17372565078952909</v>
+        <v>0.181876377314573</v>
       </c>
       <c r="F26">
-        <v>0.24983640088800041</v>
+        <v>0.1737256418912853</v>
       </c>
       <c r="G26">
-        <v>0.26413851538763522</v>
+        <v>0.2498364543060558</v>
       </c>
       <c r="H26">
-        <v>0.34651832671304778</v>
+        <v>0.2641385186240446</v>
       </c>
       <c r="I26">
-        <v>0.56103631904191142</v>
+        <v>0.3465183277842818</v>
       </c>
       <c r="J26">
-        <v>0.4707592879951894</v>
+        <v>0.5610360800383648</v>
       </c>
       <c r="K26">
-        <v>0.46544477749241581</v>
+        <v>0.4707592713050523</v>
       </c>
       <c r="L26">
-        <v>0.50728249153952687</v>
+        <v>0.4654447604286394</v>
       </c>
       <c r="M26">
-        <v>0.60040042625119705</v>
+        <v>0.5072824571536171</v>
       </c>
       <c r="N26">
-        <v>0.67248529095882148</v>
+        <v>0.6004003160134654</v>
       </c>
       <c r="O26">
-        <v>0.74230755728660336</v>
+        <v>0.6724851404055106</v>
       </c>
       <c r="P26">
-        <v>0.8495641700683384</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.7423073576474765</v>
+      </c>
+      <c r="Q26">
+        <v>0.8495639407726308</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>4.6866009934718761E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C27">
-        <v>0.19378262777558139</v>
+        <v>0.04686600666578454</v>
       </c>
       <c r="D27">
-        <v>0.1804893746848979</v>
+        <v>0.1937826312898112</v>
       </c>
       <c r="E27">
-        <v>0.17058078454246001</v>
+        <v>0.1804893725516283</v>
       </c>
       <c r="F27">
-        <v>0.2294761844080144</v>
+        <v>0.1705807664515697</v>
       </c>
       <c r="G27">
-        <v>0.23008920383029741</v>
+        <v>0.2294761859384842</v>
       </c>
       <c r="H27">
-        <v>0.2485507047849117</v>
+        <v>0.2300891988635003</v>
       </c>
       <c r="I27">
-        <v>0.40962486602914328</v>
+        <v>0.2485507132280947</v>
       </c>
       <c r="J27">
-        <v>0.34349793720711103</v>
+        <v>0.4096246102968517</v>
       </c>
       <c r="K27">
-        <v>0.29910169930474129</v>
+        <v>0.3434979353902631</v>
       </c>
       <c r="L27">
-        <v>0.29112351515597501</v>
+        <v>0.2991016768994406</v>
       </c>
       <c r="M27">
-        <v>0.34295131432125492</v>
+        <v>0.2911234833345305</v>
       </c>
       <c r="N27">
-        <v>0.35453208293590788</v>
+        <v>0.3429512680156436</v>
       </c>
       <c r="O27">
-        <v>0.40271238751335331</v>
+        <v>0.3545320420908317</v>
       </c>
       <c r="P27">
-        <v>0.43224383924651621</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.40271229035728</v>
+      </c>
+      <c r="Q27">
+        <v>0.432243734837183</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>4.211349595824581E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>0.16839320761407151</v>
+        <v>0.04211349338402404</v>
       </c>
       <c r="D28">
-        <v>0.2000593831772953</v>
+        <v>0.1683932178805827</v>
       </c>
       <c r="E28">
-        <v>0.19052697316246739</v>
+        <v>0.2000593732191474</v>
       </c>
       <c r="F28">
-        <v>0.19163771549334069</v>
+        <v>0.1905269544541258</v>
       </c>
       <c r="G28">
-        <v>0.20409619797230791</v>
+        <v>0.1916377223303448</v>
       </c>
       <c r="H28">
-        <v>0.2803837600103592</v>
+        <v>0.2040962026177143</v>
       </c>
       <c r="I28">
-        <v>0.39460201004265782</v>
+        <v>0.2803837606386805</v>
       </c>
       <c r="J28">
-        <v>0.37614285439332068</v>
+        <v>0.3946020104836495</v>
       </c>
       <c r="K28">
-        <v>0.35058602814054912</v>
+        <v>0.3761428449426468</v>
       </c>
       <c r="L28">
-        <v>0.31197423993546142</v>
+        <v>0.3505860126161559</v>
       </c>
       <c r="M28">
-        <v>0.31929242706023347</v>
+        <v>0.3119742096059304</v>
       </c>
       <c r="N28">
-        <v>0.36434400457661681</v>
+        <v>0.3192923809070075</v>
       </c>
       <c r="O28">
-        <v>0.41662832543469802</v>
+        <v>0.3643439528866944</v>
       </c>
       <c r="P28">
-        <v>0.44214266755581949</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.4166282588141453</v>
+      </c>
+      <c r="Q28">
+        <v>0.4421425780176895</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>4.4827244514998602E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>0.17805542529352969</v>
+        <v>0.04482724258902183</v>
       </c>
       <c r="D29">
-        <v>0.20903391189848861</v>
+        <v>0.1780554325909001</v>
       </c>
       <c r="E29">
-        <v>0.20358081273753631</v>
+        <v>0.2090339022603953</v>
       </c>
       <c r="F29">
-        <v>0.19925835816931811</v>
+        <v>0.2035807964406022</v>
       </c>
       <c r="G29">
-        <v>0.21133229957989819</v>
+        <v>0.1992583714834787</v>
       </c>
       <c r="H29">
-        <v>0.28351476484313071</v>
+        <v>0.2113323030793104</v>
       </c>
       <c r="I29">
-        <v>0.39925687154441741</v>
+        <v>0.2835147614430538</v>
       </c>
       <c r="J29">
-        <v>0.38786662946914241</v>
+        <v>0.3992568749851276</v>
       </c>
       <c r="K29">
-        <v>0.33293576339766762</v>
+        <v>0.3878666232655363</v>
       </c>
       <c r="L29">
-        <v>0.29413509472839028</v>
+        <v>0.3329357533324092</v>
       </c>
       <c r="M29">
-        <v>0.28733481221619078</v>
+        <v>0.2941350711071456</v>
       </c>
       <c r="N29">
-        <v>0.3297417624494044</v>
+        <v>0.2873347717465857</v>
       </c>
       <c r="O29">
-        <v>0.37137162691503522</v>
+        <v>0.3297417097821743</v>
       </c>
       <c r="P29">
-        <v>0.39071330075140331</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.3713715108084533</v>
+      </c>
+      <c r="Q29">
+        <v>0.3907132188158159</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>4.2582388048687587E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>0.1728235495530889</v>
+        <v>0.04258238520472204</v>
       </c>
       <c r="D30">
-        <v>0.2072451292569098</v>
+        <v>0.1728235631225745</v>
       </c>
       <c r="E30">
-        <v>0.19940162893287691</v>
+        <v>0.2072451231245894</v>
       </c>
       <c r="F30">
-        <v>0.2012615744996937</v>
+        <v>0.1994016117613373</v>
       </c>
       <c r="G30">
-        <v>0.20804919405558789</v>
+        <v>0.2012615841910732</v>
       </c>
       <c r="H30">
-        <v>0.29401886604057992</v>
+        <v>0.2080491950738701</v>
       </c>
       <c r="I30">
-        <v>0.40841780206884609</v>
+        <v>0.2940188683130099</v>
       </c>
       <c r="J30">
-        <v>0.39712597415366868</v>
+        <v>0.408417822304632</v>
       </c>
       <c r="K30">
-        <v>0.33719810849179321</v>
+        <v>0.3971259811920191</v>
       </c>
       <c r="L30">
-        <v>0.29971314553586942</v>
+        <v>0.3371981028258151</v>
       </c>
       <c r="M30">
-        <v>0.29325001000249712</v>
+        <v>0.2997131270700171</v>
       </c>
       <c r="N30">
-        <v>0.33598354446719292</v>
+        <v>0.2932499748314366</v>
       </c>
       <c r="O30">
-        <v>0.37085353046669289</v>
+        <v>0.3359835095058581</v>
       </c>
       <c r="P30">
-        <v>0.38228123576679052</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.3708534922836574</v>
+      </c>
+      <c r="Q30">
+        <v>0.3822811824314091</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>4.6681548562926951E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>0.17425611636893809</v>
+        <v>0.04668154753350788</v>
       </c>
       <c r="D31">
-        <v>0.204116266617341</v>
+        <v>0.1742561226866325</v>
       </c>
       <c r="E31">
-        <v>0.19476625658934671</v>
+        <v>0.2041162571743317</v>
       </c>
       <c r="F31">
-        <v>0.19445513808551479</v>
+        <v>0.194766235809601</v>
       </c>
       <c r="G31">
-        <v>0.19956656973244269</v>
+        <v>0.1944551486073679</v>
       </c>
       <c r="H31">
-        <v>0.27271518007347051</v>
+        <v>0.1995665681726033</v>
       </c>
       <c r="I31">
-        <v>0.38044528844633002</v>
+        <v>0.2727151773054953</v>
       </c>
       <c r="J31">
-        <v>0.37413350623707442</v>
+        <v>0.3804452852755754</v>
       </c>
       <c r="K31">
-        <v>0.33483193815083861</v>
+        <v>0.3741335037501045</v>
       </c>
       <c r="L31">
-        <v>0.29200916300835528</v>
+        <v>0.3348319320391802</v>
       </c>
       <c r="M31">
-        <v>0.28050290743325179</v>
+        <v>0.2920091457652737</v>
       </c>
       <c r="N31">
-        <v>0.31489993737410671</v>
+        <v>0.28050288428595</v>
       </c>
       <c r="O31">
-        <v>0.36329223722445408</v>
+        <v>0.3148999051642867</v>
       </c>
       <c r="P31">
-        <v>0.36786247058707039</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.3632922622475775</v>
+      </c>
+      <c r="Q31">
+        <v>0.3678624415677606</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>4.4212167943294862E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>0.1771401563336123</v>
+        <v>0.04421216545016377</v>
       </c>
       <c r="D32">
-        <v>0.21126807851294599</v>
+        <v>0.177140161320322</v>
       </c>
       <c r="E32">
-        <v>0.2062935334679489</v>
+        <v>0.2112680683091249</v>
       </c>
       <c r="F32">
-        <v>0.20341998389180929</v>
+        <v>0.2062935159586587</v>
       </c>
       <c r="G32">
-        <v>0.21327167508060579</v>
+        <v>0.2034199839744701</v>
       </c>
       <c r="H32">
-        <v>0.30523067385558827</v>
+        <v>0.2132716760333195</v>
       </c>
       <c r="I32">
-        <v>0.40243597137035481</v>
+        <v>0.3052306724509476</v>
       </c>
       <c r="J32">
-        <v>0.38860894777145399</v>
+        <v>0.4024359720590023</v>
       </c>
       <c r="K32">
-        <v>0.36562841590156808</v>
+        <v>0.388608939045658</v>
       </c>
       <c r="L32">
-        <v>0.32628207748539251</v>
+        <v>0.3656283956798188</v>
       </c>
       <c r="M32">
-        <v>0.32822848788765119</v>
+        <v>0.3262820361930742</v>
       </c>
       <c r="N32">
-        <v>0.38439910109148101</v>
+        <v>0.3282284286553995</v>
       </c>
       <c r="O32">
-        <v>0.45371211201523293</v>
+        <v>0.3843990367493472</v>
       </c>
       <c r="P32">
-        <v>0.50175986341143319</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.4537120176583442</v>
+      </c>
+      <c r="Q32">
+        <v>0.5017597126599815</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>4.5505479042098597E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>0.18211925653649599</v>
+        <v>0.045505476149354</v>
       </c>
       <c r="D33">
-        <v>0.21719834197757251</v>
+        <v>0.1821192720672157</v>
       </c>
       <c r="E33">
-        <v>0.20948319316459019</v>
+        <v>0.2171983333641993</v>
       </c>
       <c r="F33">
-        <v>0.2039044279186091</v>
+        <v>0.2094831723028805</v>
       </c>
       <c r="G33">
-        <v>0.21654943762401349</v>
+        <v>0.2039044415724223</v>
       </c>
       <c r="H33">
-        <v>0.30233631196510807</v>
+        <v>0.2165494453072278</v>
       </c>
       <c r="I33">
-        <v>0.40547579228871689</v>
+        <v>0.3023363128636211</v>
       </c>
       <c r="J33">
-        <v>0.39234386527550352</v>
+        <v>0.4054758029177523</v>
       </c>
       <c r="K33">
-        <v>0.34928797865364408</v>
+        <v>0.3923438602103058</v>
       </c>
       <c r="L33">
-        <v>0.31851012340609791</v>
+        <v>0.3492879648878869</v>
       </c>
       <c r="M33">
-        <v>0.31973847067991878</v>
+        <v>0.3185100889214179</v>
       </c>
       <c r="N33">
-        <v>0.37548588729120441</v>
+        <v>0.3197384246536338</v>
       </c>
       <c r="O33">
-        <v>0.43675684513612772</v>
+        <v>0.3754858238364089</v>
       </c>
       <c r="P33">
-        <v>0.48912963705861368</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.4367567573532382</v>
+      </c>
+      <c r="Q33">
+        <v>0.4891295237303574</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>4.535176491416161E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>0.17755199433468799</v>
+        <v>0.04535176128083638</v>
       </c>
       <c r="D34">
-        <v>0.2122463128530851</v>
+        <v>0.1775520004653702</v>
       </c>
       <c r="E34">
-        <v>0.20664300573729399</v>
+        <v>0.2122463020914206</v>
       </c>
       <c r="F34">
-        <v>0.20328130922138421</v>
+        <v>0.2066429871595917</v>
       </c>
       <c r="G34">
-        <v>0.20990030642231289</v>
+        <v>0.2032812827368093</v>
       </c>
       <c r="H34">
-        <v>0.28885583296532941</v>
+        <v>0.2099003115747533</v>
       </c>
       <c r="I34">
-        <v>0.39738020115010653</v>
+        <v>0.2888558384345528</v>
       </c>
       <c r="J34">
-        <v>0.39319053381730262</v>
+        <v>0.3973801867365796</v>
       </c>
       <c r="K34">
-        <v>0.36514740091727099</v>
+        <v>0.3931905258142883</v>
       </c>
       <c r="L34">
-        <v>0.32536404830444199</v>
+        <v>0.3651473797769528</v>
       </c>
       <c r="M34">
-        <v>0.31698250748339862</v>
+        <v>0.3253640112332257</v>
       </c>
       <c r="N34">
-        <v>0.36328176519762728</v>
+        <v>0.3169824571942366</v>
       </c>
       <c r="O34">
-        <v>0.42075322473785232</v>
+        <v>0.3632817059417103</v>
       </c>
       <c r="P34">
-        <v>0.45703131123563412</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.4207531459573088</v>
+      </c>
+      <c r="Q34">
+        <v>0.4570312119696071</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>4.3226666622369223E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>0.1764129593200581</v>
+        <v>0.04322666433182613</v>
       </c>
       <c r="D35">
-        <v>0.21007234646717499</v>
+        <v>0.1764129662456544</v>
       </c>
       <c r="E35">
-        <v>0.2044396313880287</v>
+        <v>0.2100723361247092</v>
       </c>
       <c r="F35">
-        <v>0.20550375220789691</v>
+        <v>0.2044396129616226</v>
       </c>
       <c r="G35">
-        <v>0.21365695896125311</v>
+        <v>0.2055037651718635</v>
       </c>
       <c r="H35">
-        <v>0.28694101428477797</v>
+        <v>0.2136569855074017</v>
       </c>
       <c r="I35">
-        <v>0.38983997704522261</v>
+        <v>0.2869410018465491</v>
       </c>
       <c r="J35">
-        <v>0.3810601092524209</v>
+        <v>0.3898399815662091</v>
       </c>
       <c r="K35">
-        <v>0.34242703566154847</v>
+        <v>0.3810601073111144</v>
       </c>
       <c r="L35">
-        <v>0.30444206491087072</v>
+        <v>0.3424270284468339</v>
       </c>
       <c r="M35">
-        <v>0.29706435849936041</v>
+        <v>0.3044420424456901</v>
       </c>
       <c r="N35">
-        <v>0.33921778633555227</v>
+        <v>0.2970643190545115</v>
       </c>
       <c r="O35">
-        <v>0.39043592724883658</v>
+        <v>0.3392177514350052</v>
       </c>
       <c r="P35">
-        <v>0.4246987272411783</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.3904358792379438</v>
+      </c>
+      <c r="Q35">
+        <v>0.4246986516805656</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>4.5158369765544062E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>0.17998507381897</v>
+        <v>0.04515836337233518</v>
       </c>
       <c r="D36">
-        <v>0.21531338376472761</v>
+        <v>0.1799850771223796</v>
       </c>
       <c r="E36">
-        <v>0.2060357217781667</v>
+        <v>0.2153133750060784</v>
       </c>
       <c r="F36">
-        <v>0.2018327612738248</v>
+        <v>0.206035709784144</v>
       </c>
       <c r="G36">
-        <v>0.20581834882753119</v>
+        <v>0.2018327673671118</v>
       </c>
       <c r="H36">
-        <v>0.2807242508363712</v>
+        <v>0.2058183389227924</v>
       </c>
       <c r="I36">
-        <v>0.37803662897243973</v>
+        <v>0.2807242904378217</v>
       </c>
       <c r="J36">
-        <v>0.37674078261705901</v>
+        <v>0.378036629696948</v>
       </c>
       <c r="K36">
-        <v>0.33960986406338822</v>
+        <v>0.3767407862738371</v>
       </c>
       <c r="L36">
-        <v>0.31009258047676569</v>
+        <v>0.3396098585871994</v>
       </c>
       <c r="M36">
-        <v>0.28942747592699419</v>
+        <v>0.3100925666179127</v>
       </c>
       <c r="N36">
-        <v>0.31225995938357648</v>
+        <v>0.289427448640702</v>
       </c>
       <c r="O36">
-        <v>0.35989239798988282</v>
+        <v>0.3122599193924065</v>
       </c>
       <c r="P36">
-        <v>0.37093922601934309</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.3598923581223673</v>
+      </c>
+      <c r="Q36">
+        <v>0.3709391820399553</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>5.2182177506884253E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C37">
-        <v>0.30543514924227472</v>
+        <v>0.05218217140329062</v>
       </c>
       <c r="D37">
-        <v>0.27571231646660749</v>
+        <v>0.3054351888359967</v>
       </c>
       <c r="E37">
-        <v>0.30264364698466018</v>
+        <v>0.2757122857954656</v>
       </c>
       <c r="F37">
-        <v>0.48487255528091888</v>
+        <v>0.3026436226832337</v>
       </c>
       <c r="G37">
-        <v>0.55786361603383239</v>
+        <v>0.4848725774058664</v>
       </c>
       <c r="H37">
-        <v>0.58220123419083614</v>
+        <v>0.5578635957972331</v>
       </c>
       <c r="I37">
-        <v>0.5954722690002765</v>
+        <v>0.5822010929723748</v>
       </c>
       <c r="J37">
-        <v>0.63636047789801731</v>
+        <v>0.595472095438852</v>
       </c>
       <c r="K37">
-        <v>0.67466514213101869</v>
+        <v>0.6363602956020341</v>
       </c>
       <c r="L37">
-        <v>0.7242395462425093</v>
+        <v>0.6746650419206246</v>
       </c>
       <c r="M37">
-        <v>0.79868911376136276</v>
+        <v>0.7242393643696317</v>
       </c>
       <c r="N37">
-        <v>0.78899007949393096</v>
+        <v>0.7986856505167174</v>
       </c>
       <c r="O37">
-        <v>0.78327446142851687</v>
+        <v>0.788989950418361</v>
       </c>
       <c r="P37">
-        <v>0.77907360308833162</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.7832741715345455</v>
+      </c>
+      <c r="Q37">
+        <v>0.7790731385596557</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>4.7296092955685258E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C38">
-        <v>0.22926865658027351</v>
+        <v>0.04729608758931946</v>
       </c>
       <c r="D38">
-        <v>0.226809746544264</v>
+        <v>0.2292686894723816</v>
       </c>
       <c r="E38">
-        <v>0.27280878442404438</v>
+        <v>0.2268097407660066</v>
       </c>
       <c r="F38">
-        <v>0.38360148767232949</v>
+        <v>0.2728088131149841</v>
       </c>
       <c r="G38">
-        <v>0.36053041958921961</v>
+        <v>0.3836015029680007</v>
       </c>
       <c r="H38">
-        <v>0.26554790358197888</v>
+        <v>0.3605304289771045</v>
       </c>
       <c r="I38">
-        <v>0.32464749236925938</v>
+        <v>0.2655478920054845</v>
       </c>
       <c r="J38">
-        <v>0.41723027793056422</v>
+        <v>0.3246474284273111</v>
       </c>
       <c r="K38">
-        <v>0.46735594900722249</v>
+        <v>0.4172301722590468</v>
       </c>
       <c r="L38">
-        <v>0.50126693721420956</v>
+        <v>0.4673558202628041</v>
       </c>
       <c r="M38">
-        <v>0.53334832094935847</v>
+        <v>0.5012667733145335</v>
       </c>
       <c r="N38">
-        <v>0.53806970937910359</v>
+        <v>0.5333481718961945</v>
       </c>
       <c r="O38">
-        <v>0.54968173045164481</v>
+        <v>0.5380696421271886</v>
       </c>
       <c r="P38">
-        <v>0.5661758356559895</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.5496816155673032</v>
+      </c>
+      <c r="Q38">
+        <v>0.5661757073239798</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>4.9029678666618698E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C39">
-        <v>0.2255963730668171</v>
+        <v>0.04902967896668076</v>
       </c>
       <c r="D39">
-        <v>0.2130788244235447</v>
+        <v>0.2255963986618301</v>
       </c>
       <c r="E39">
-        <v>0.22322455484701251</v>
+        <v>0.2130788296582954</v>
       </c>
       <c r="F39">
-        <v>0.30781716624645988</v>
+        <v>0.2232246482363181</v>
       </c>
       <c r="G39">
-        <v>0.29339340681274101</v>
+        <v>0.3078174107721697</v>
       </c>
       <c r="H39">
-        <v>0.25363966465276122</v>
+        <v>0.2933934187785797</v>
       </c>
       <c r="I39">
-        <v>0.29190198959078989</v>
+        <v>0.2536396616583804</v>
       </c>
       <c r="J39">
-        <v>0.34759398137579761</v>
+        <v>0.2919021339105003</v>
       </c>
       <c r="K39">
-        <v>0.36653656431462739</v>
+        <v>0.347594043969</v>
       </c>
       <c r="L39">
-        <v>0.39699726786775502</v>
+        <v>0.3665364981270804</v>
       </c>
       <c r="M39">
-        <v>0.40508446177099389</v>
+        <v>0.3969972109648515</v>
       </c>
       <c r="N39">
-        <v>0.44567883868674579</v>
+        <v>0.4050843876692884</v>
       </c>
       <c r="O39">
-        <v>0.48611755469402312</v>
+        <v>0.4456787294021464</v>
       </c>
       <c r="P39">
-        <v>0.51294198020782478</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.486117440548065</v>
+      </c>
+      <c r="Q39">
+        <v>0.5129418218902307</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>7.6902923184229699E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C40">
-        <v>0.12841731980223409</v>
+        <v>0.07690291207962101</v>
       </c>
       <c r="D40">
-        <v>0.2129539871055694</v>
+        <v>0.1284173209657612</v>
       </c>
       <c r="E40">
-        <v>0.27540052019382322</v>
+        <v>0.2129539940865476</v>
       </c>
       <c r="F40">
-        <v>0.3547200493242238</v>
+        <v>0.2754005360549369</v>
       </c>
       <c r="G40">
-        <v>0.37198495433414769</v>
+        <v>0.3547200674667461</v>
       </c>
       <c r="H40">
-        <v>0.46221637996410331</v>
+        <v>0.3719849205417461</v>
       </c>
       <c r="I40">
-        <v>0.5940245660190655</v>
+        <v>0.46221630979911</v>
       </c>
       <c r="J40">
-        <v>0.62188482793877942</v>
+        <v>0.5940244131177848</v>
       </c>
       <c r="K40">
-        <v>0.62060106476957588</v>
+        <v>0.6218847295008809</v>
       </c>
       <c r="L40">
-        <v>0.63299291912329303</v>
+        <v>0.6206009006088405</v>
       </c>
       <c r="M40">
-        <v>0.62758018157849393</v>
+        <v>0.6329928468830467</v>
       </c>
       <c r="N40">
-        <v>0.65378350984436295</v>
+        <v>0.6275801053946441</v>
       </c>
       <c r="O40">
-        <v>0.70693998816298831</v>
+        <v>0.6537833041589077</v>
       </c>
       <c r="P40">
-        <v>0.78766504909410973</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.7069396847835099</v>
+      </c>
+      <c r="Q40">
+        <v>0.7876645815597241</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.10916726126708549</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C41">
-        <v>0.44397830868153643</v>
+        <v>0.1091672577519001</v>
       </c>
       <c r="D41">
-        <v>0.50771809070157414</v>
+        <v>0.4439783158325811</v>
       </c>
       <c r="E41">
-        <v>0.62785109359541025</v>
+        <v>0.5077180808891482</v>
       </c>
       <c r="F41">
-        <v>0.64748939648289039</v>
+        <v>0.6278510830034636</v>
       </c>
       <c r="G41">
-        <v>0.6874775733687829</v>
+        <v>0.6474893930845419</v>
       </c>
       <c r="H41">
-        <v>0.72689472633727858</v>
+        <v>0.6874775788660985</v>
       </c>
       <c r="I41">
-        <v>0.68707803499460252</v>
+        <v>0.7268947429833162</v>
       </c>
       <c r="J41">
-        <v>0.76255262608284524</v>
+        <v>0.6870780502134458</v>
       </c>
       <c r="K41">
-        <v>0.83232878195953575</v>
+        <v>0.7625526562841012</v>
       </c>
       <c r="L41">
-        <v>0.85027807545871437</v>
+        <v>0.8323288132976613</v>
       </c>
       <c r="M41">
-        <v>0.91768821081186791</v>
+        <v>0.8502780502220396</v>
       </c>
       <c r="N41">
-        <v>0.99977819871984952</v>
+        <v>0.9176881408284869</v>
       </c>
       <c r="O41">
-        <v>1.018662539929776</v>
+        <v>0.9997781388224183</v>
       </c>
       <c r="P41">
-        <v>1.0467001420543851</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>1.018662455517695</v>
+      </c>
+      <c r="Q41">
+        <v>1.046700057176173</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>6.5142627660439156E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C42">
-        <v>0.20208976074397261</v>
+        <v>0.06514262773698765</v>
       </c>
       <c r="D42">
-        <v>0.53357475935146637</v>
+        <v>0.2020897461758518</v>
       </c>
       <c r="E42">
-        <v>0.43931685126454129</v>
+        <v>0.5335748170916637</v>
       </c>
       <c r="F42">
-        <v>0.43842701297349479</v>
+        <v>0.4393168527337821</v>
       </c>
       <c r="G42">
-        <v>0.45854462066192048</v>
+        <v>0.4384270187732364</v>
       </c>
       <c r="H42">
-        <v>0.39977133186597219</v>
+        <v>0.4585446526473915</v>
       </c>
       <c r="I42">
-        <v>0.43443645867027531</v>
+        <v>0.3997713506993504</v>
       </c>
       <c r="J42">
-        <v>0.47581900052944281</v>
+        <v>0.4344364523387005</v>
       </c>
       <c r="K42">
-        <v>0.45736368340531058</v>
+        <v>0.4758190267436213</v>
       </c>
       <c r="L42">
-        <v>0.47626753994997362</v>
+        <v>0.457363708036322</v>
       </c>
       <c r="M42">
-        <v>0.52044329814833579</v>
+        <v>0.4762675625586764</v>
       </c>
       <c r="N42">
-        <v>0.55528411181354642</v>
+        <v>0.5204433054034319</v>
       </c>
       <c r="O42">
-        <v>0.56253082501378415</v>
+        <v>0.5552841153219541</v>
       </c>
       <c r="P42">
-        <v>0.59396558384529841</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.5625308080510537</v>
+      </c>
+      <c r="Q42">
+        <v>0.5939656263075492</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>5.6621402640376101E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C43">
-        <v>0.23776440477484159</v>
+        <v>0.05662140142185081</v>
       </c>
       <c r="D43">
-        <v>0.39399949844648041</v>
+        <v>0.2377644142609703</v>
       </c>
       <c r="E43">
-        <v>0.40589939890633309</v>
+        <v>0.3939994734392138</v>
       </c>
       <c r="F43">
-        <v>0.35953529952127339</v>
+        <v>0.4058993863375903</v>
       </c>
       <c r="G43">
-        <v>0.36945234516268921</v>
+        <v>0.3595353104061157</v>
       </c>
       <c r="H43">
-        <v>0.37534985076639071</v>
+        <v>0.3694523501965644</v>
       </c>
       <c r="I43">
-        <v>0.4203814515417163</v>
+        <v>0.3753498618528228</v>
       </c>
       <c r="J43">
-        <v>0.51187531349184878</v>
+        <v>0.4203814565909297</v>
       </c>
       <c r="K43">
-        <v>0.5245405488884588</v>
+        <v>0.5118753401866893</v>
       </c>
       <c r="L43">
-        <v>0.5450837749492794</v>
+        <v>0.52454054577539</v>
       </c>
       <c r="M43">
-        <v>0.57995924391190212</v>
+        <v>0.54508376235778</v>
       </c>
       <c r="N43">
-        <v>0.61961779170056508</v>
+        <v>0.5799592122182085</v>
       </c>
       <c r="O43">
-        <v>0.66365780750112591</v>
+        <v>0.6196177367641263</v>
       </c>
       <c r="P43">
-        <v>0.69605406817007354</v>
+        <v>0.6636577287539913</v>
+      </c>
+      <c r="Q43">
+        <v>0.6960539563399093</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P43">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>0.2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>0.2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>